--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-13.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-13.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261009" sheetId="1" r:id="R4e9ad451f6cd4e69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261009" sheetId="1" r:id="R3272a03342134ddd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-13.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-13.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261009" sheetId="1" r:id="R3272a03342134ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261012" sheetId="1" r:id="Rf10a3d6026324829"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="174">
   <x:si>
-    <x:t>Daily Holdings (%)  10/09/2026</x:t>
+    <x:t>Daily Holdings (%)  10/12/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -52,19 +52,19 @@
     <x:t>BBG000BBJQV0</x:t>
   </x:si>
   <x:si>
-    <x:t>62,152,997</x:t>
+    <x:t>62,436,533</x:t>
   </x:si>
   <x:si>
     <x:t>Stock</x:t>
   </x:si>
   <x:si>
-    <x:t>$14,250,439,152.16</x:t>
+    <x:t>$14,130,636,148.56</x:t>
   </x:si>
   <x:si>
     <x:t> -- </x:t>
   </x:si>
   <x:si>
-    <x:t>19.60%</x:t>
+    <x:t>19.77%</x:t>
   </x:si>
   <x:si>
     <x:t>TSM</x:t>
@@ -76,13 +76,13 @@
     <x:t>BBG000BD8ZK0</x:t>
   </x:si>
   <x:si>
-    <x:t>14,851,325</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$6,732,254,135.75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.26%</x:t>
+    <x:t>14,919,074</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$6,629,290,531.90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.27%</x:t>
   </x:si>
   <x:si>
     <x:t>AMD</x:t>
@@ -94,13 +94,13 @@
     <x:t>BBG000BBQCY0</x:t>
   </x:si>
   <x:si>
-    <x:t>6,669,492</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$4,055,718,085.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.58%</x:t>
+    <x:t>6,699,918</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,981,359,272.32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.57%</x:t>
   </x:si>
   <x:si>
     <x:t>AVGO</x:t>
@@ -112,13 +112,31 @@
     <x:t>BBG00KHY5S69</x:t>
   </x:si>
   <x:si>
-    <x:t>10,843,864</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,920,490,590.56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.39%</x:t>
+    <x:t>10,893,452</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,864,234,227.96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.41%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TXN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Texas Instruments Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BVV7G1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11,983,521</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,376,237,206.54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.72%</x:t>
   </x:si>
   <x:si>
     <x:t>MU</x:t>
@@ -130,13 +148,31 @@
     <x:t>BBG000C5Z1S3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,381,564</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,479,629,356.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.79%</x:t>
+    <x:t>3,396,986</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,359,755,033.44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.70%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Applied Materials Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BBPFB9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6,686,086</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,326,528,367.58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.65%</x:t>
   </x:si>
   <x:si>
     <x:t>MRVL</x:t>
@@ -148,49 +184,13 @@
     <x:t>BBG00ZXBJ153</x:t>
   </x:si>
   <x:si>
-    <x:t>12,400,061</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,413,488,792.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.70%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TXN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texas Instruments Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BVV7G1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11,928,972</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,384,726,515.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.66%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Applied Materials Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BBPFB9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6,655,649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,374,613,712.47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.64%</x:t>
+    <x:t>12,456,623</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,311,717,790.78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.63%</x:t>
   </x:si>
   <x:si>
     <x:t>KLAC</x:t>
@@ -202,13 +202,13 @@
     <x:t>BBG000BMTFR4</x:t>
   </x:si>
   <x:si>
-    <x:t>17,060,342</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,336,491,084.94</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.59%</x:t>
+    <x:t>17,138,354</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,258,343,862.48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.56%</x:t>
   </x:si>
   <x:si>
     <x:t>ASML</x:t>
@@ -220,13 +220,13 @@
     <x:t>BBG000K6MRN4</x:t>
   </x:si>
   <x:si>
-    <x:t>1,808,529</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,219,796,519.86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.43%</x:t>
+    <x:t>1,816,779</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,179,799,276.96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.45%</x:t>
   </x:si>
   <x:si>
     <x:t>LRCX</x:t>
@@ -238,13 +238,31 @@
     <x:t>BBG000BNFLM9</x:t>
   </x:si>
   <x:si>
-    <x:t>9,880,037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,150,150,997.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.33%</x:t>
+    <x:t>9,925,214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,072,449,245.84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.30%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Analog Devices Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BB6G37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,516,826</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,053,672,978.37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.27%</x:t>
   </x:si>
   <x:si>
     <x:t>INTC</x:t>
@@ -256,28 +274,10 @@
     <x:t>BBG000C0G1D1</x:t>
   </x:si>
   <x:si>
-    <x:t>29,372,190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,075,268,293.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.23%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Analog Devices Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BB6G37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,482,616</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,039,363,793.04</x:t>
+    <x:t>29,506,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,990,483,775.00</x:t>
   </x:si>
   <x:si>
     <x:t>4.18%</x:t>
@@ -292,13 +292,13 @@
     <x:t>BBG0238L5JS9</x:t>
   </x:si>
   <x:si>
-    <x:t>17,497,058</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,957,527,713.74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.07%</x:t>
+    <x:t>17,576,874</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,851,496,269.02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.99%</x:t>
   </x:si>
   <x:si>
     <x:t>QCOM</x:t>
@@ -310,13 +310,13 @@
     <x:t>BBG000CGC1X8</x:t>
   </x:si>
   <x:si>
-    <x:t>14,812,699</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,599,628,674.50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.58%</x:t>
+    <x:t>14,880,437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,595,594,625.91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.63%</x:t>
   </x:si>
   <x:si>
     <x:t>SNPS</x:t>
@@ -328,13 +328,13 @@
     <x:t>BBG000BSFRF3</x:t>
   </x:si>
   <x:si>
-    <x:t>2,995,764</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,527,809,682.36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.10%</x:t>
+    <x:t>3,009,459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,512,283,242.09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.12%</x:t>
   </x:si>
   <x:si>
     <x:t>CDNS</x:t>
@@ -346,13 +346,13 @@
     <x:t>BBG000C13CD9</x:t>
   </x:si>
   <x:si>
-    <x:t>4,252,603</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,500,488,442.52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.06%</x:t>
+    <x:t>4,272,051</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,488,468,009.42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.08%</x:t>
   </x:si>
   <x:si>
     <x:t>TER</x:t>
@@ -364,13 +364,13 @@
     <x:t>BBG000BV4DR6</x:t>
   </x:si>
   <x:si>
-    <x:t>2,294,965</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$924,136,506.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.27%</x:t>
+    <x:t>2,305,459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$884,950,437.15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.24%</x:t>
   </x:si>
   <x:si>
     <x:t>MPWR</x:t>
@@ -382,13 +382,13 @@
     <x:t>BBG000C30L48</x:t>
   </x:si>
   <x:si>
-    <x:t>646,428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$896,136,672.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.23%</x:t>
+    <x:t>649,387</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$856,690,812.01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.20%</x:t>
   </x:si>
   <x:si>
     <x:t>ALAB</x:t>
@@ -400,13 +400,13 @@
     <x:t>BBG00TDKHW99</x:t>
   </x:si>
   <x:si>
-    <x:t>2,315,114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$792,255,161.94</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.09%</x:t>
+    <x:t>2,325,696</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$753,781,330.56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.05%</x:t>
   </x:si>
   <x:si>
     <x:t>ARM</x:t>
@@ -418,13 +418,13 @@
     <x:t>BBG01J1GXZF0</x:t>
   </x:si>
   <x:si>
-    <x:t>2,850,443</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$759,015,962.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.04%</x:t>
+    <x:t>2,863,478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$730,874,124.72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.02%</x:t>
   </x:si>
   <x:si>
     <x:t>NXPI</x:t>
@@ -436,13 +436,13 @@
     <x:t>BBG000BND699</x:t>
   </x:si>
   <x:si>
-    <x:t>3,128,502</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$711,796,775.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.98%</x:t>
+    <x:t>3,142,813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$707,792,915.73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.99%</x:t>
   </x:si>
   <x:si>
     <x:t>STM</x:t>
@@ -454,13 +454,13 @@
     <x:t>BBG000BD4GX2</x:t>
   </x:si>
   <x:si>
-    <x:t>12,508,308</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$651,182,514.48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.90%</x:t>
+    <x:t>12,565,508</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$634,306,843.84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.89%</x:t>
   </x:si>
   <x:si>
     <x:t>MCHP</x:t>
@@ -472,10 +472,10 @@
     <x:t>BBG000BHCP19</x:t>
   </x:si>
   <x:si>
-    <x:t>7,349,895</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$555,284,567.25</x:t>
+    <x:t>7,383,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$545,123,805.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.76%</x:t>
@@ -490,10 +490,10 @@
     <x:t>BBG000DV7MX4</x:t>
   </x:si>
   <x:si>
-    <x:t>4,527,310</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$351,002,344.30</x:t>
+    <x:t>4,548,012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$345,648,912.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.48%</x:t>
@@ -505,13 +505,13 @@
     <x:t> </x:t>
   </x:si>
   <x:si>
-    <x:t>39,216,955</x:t>
+    <x:t>39,212,349</x:t>
   </x:si>
   <x:si>
     <x:t>Cash Bal</x:t>
   </x:si>
   <x:si>
-    <x:t>$39,216,955.08</x:t>
+    <x:t>$39,212,348.95</x:t>
   </x:si>
   <x:si>
     <x:t>0.05%</x:t>
@@ -523,7 +523,7 @@
     <x:t>Cash</x:t>
   </x:si>
   <x:si>
-    <x:t>$-1,234,969.86</x:t>
+    <x:t>$-3,295,782.93</x:t>
   </x:si>
   <x:si>
     <x:t>-0.00%</x:t>
